--- a/diseases/d057/2015-2019.xlsx
+++ b/diseases/d057/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1502,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2245,9 +2239,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2976,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3873,9 +3861,6 @@
       <c r="O23" t="n">
         <v>7</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.01372982141631091</v>
       </c>
@@ -4613,9 +4598,6 @@
       <c r="O28" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.01961403059472987</v>
       </c>
@@ -5353,9 +5335,6 @@
       <c r="O33" t="n">
         <v>16</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.03138244895156779</v>
       </c>
@@ -6241,9 +6220,6 @@
       <c r="O39" t="n">
         <v>13</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.02549823977314883</v>
       </c>
@@ -6981,9 +6957,6 @@
       <c r="O44" t="n">
         <v>16</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.03138244895156779</v>
       </c>
@@ -7721,9 +7694,6 @@
       <c r="O49" t="n">
         <v>15</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.0294210458920948</v>
       </c>
@@ -8609,9 +8579,6 @@
       <c r="O55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.003922806118945974</v>
       </c>
@@ -9349,9 +9316,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -10237,9 +10201,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10977,9 +10938,6 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.00194939985678539</v>
       </c>
@@ -11717,9 +11675,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12605,9 +12560,6 @@
       <c r="O82" t="n">
         <v>3</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.00584819957035617</v>
       </c>
@@ -13345,9 +13297,6 @@
       <c r="O87" t="n">
         <v>10</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.0194939985678539</v>
       </c>
@@ -14085,9 +14034,6 @@
       <c r="O92" t="n">
         <v>13</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.02534219813821007</v>
       </c>
@@ -14973,9 +14919,6 @@
       <c r="O98" t="n">
         <v>18</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.03508919742213702</v>
       </c>
@@ -15713,9 +15656,6 @@
       <c r="O103" t="n">
         <v>18</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.03508919742213702</v>
       </c>
@@ -16453,9 +16393,6 @@
       <c r="O108" t="n">
         <v>34</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.06627959513070326</v>
       </c>
@@ -17341,9 +17278,6 @@
       <c r="O114" t="n">
         <v>62</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.1208627911206942</v>
       </c>
@@ -18081,9 +18015,6 @@
       <c r="O119" t="n">
         <v>6</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.01169639914071234</v>
       </c>
@@ -18821,9 +18752,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -19709,9 +19637,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -20449,9 +20374,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -21189,9 +21111,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -22077,9 +21996,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -22817,9 +22733,6 @@
       <c r="O151" t="n">
         <v>15</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.02913398048514701</v>
       </c>
@@ -23557,9 +23470,6 @@
       <c r="O156" t="n">
         <v>34</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.06603702243299987</v>
       </c>
@@ -24445,9 +24355,6 @@
       <c r="O162" t="n">
         <v>45</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.08740194145544102</v>
       </c>
@@ -25185,9 +25092,6 @@
       <c r="O167" t="n">
         <v>47</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.09128647218679395</v>
       </c>
@@ -26073,9 +25977,6 @@
       <c r="O173" t="n">
         <v>49</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.09517100291814688</v>
       </c>
@@ -26813,9 +26714,6 @@
       <c r="O178" t="n">
         <v>79</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.1534389638884409</v>
       </c>
@@ -27553,9 +27451,6 @@
       <c r="O183" t="n">
         <v>3</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.005826796097029401</v>
       </c>
@@ -28441,9 +28336,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -29181,9 +29073,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -29921,9 +29810,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -30661,9 +30547,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -31549,9 +31432,6 @@
       <c r="O210" t="n">
         <v>4</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.00774579928844764</v>
       </c>
@@ -32289,9 +32169,6 @@
       <c r="O215" t="n">
         <v>21</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.04066544626435011</v>
       </c>
@@ -33177,9 +33054,6 @@
       <c r="O221" t="n">
         <v>49</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.09488604128348359</v>
       </c>
@@ -33917,9 +33791,6 @@
       <c r="O226" t="n">
         <v>49</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.09488604128348359</v>
       </c>
@@ -34657,9 +34528,6 @@
       <c r="O231" t="n">
         <v>29</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.05615704484124539</v>
       </c>
@@ -35545,9 +35413,6 @@
       <c r="O237" t="n">
         <v>39</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.07552154306236449</v>
       </c>
@@ -36285,9 +36150,6 @@
       <c r="O242" t="n">
         <v>67</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.129742138081498</v>
       </c>
@@ -37025,9 +36887,6 @@
       <c r="O247" t="n">
         <v>1</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -37913,9 +37772,6 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -38653,9 +38509,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -39541,9 +39394,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -40281,9 +40131,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -41021,9 +40868,6 @@
       <c r="O274" t="n">
         <v>1</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -41761,9 +41605,6 @@
       <c r="O279" t="n">
         <v>11</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.02124871102421376</v>
       </c>
@@ -42649,9 +42490,6 @@
       <c r="O285" t="n">
         <v>34</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.06567783407484251</v>
       </c>
@@ -43389,9 +43227,6 @@
       <c r="O290" t="n">
         <v>46</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.08885824610125752</v>
       </c>
@@ -44129,9 +43964,6 @@
       <c r="O295" t="n">
         <v>45</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.08692654509905628</v>
       </c>
@@ -45017,9 +44849,6 @@
       <c r="O301" t="n">
         <v>35</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.06760953507704377</v>
       </c>
@@ -45757,9 +45586,6 @@
       <c r="O306" t="n">
         <v>51</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.09851675111226378</v>
       </c>
@@ -46645,9 +46471,6 @@
       <c r="O312" t="n">
         <v>0</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0</v>
       </c>
@@ -47383,9 +47206,6 @@
         <v>0</v>
       </c>
       <c r="O317" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q317" t="n">
         <v>0</v>
       </c>
       <c r="R317" t="n">
